--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model_info[生物模型详情信息] .xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model_info[生物模型详情信息] .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureModelInfo" sheetId="1" r:id="rId1"/>
@@ -2377,7 +2377,7 @@
     <col min="1" max="1" width="12.625" customWidth="1"/>
     <col min="2" max="2" width="23.25" customWidth="1"/>
     <col min="3" max="3" width="20.375" customWidth="1"/>
-    <col min="4" max="4" width="56" customWidth="1"/>
+    <col min="4" max="4" width="113" customWidth="1"/>
     <col min="5" max="5" width="33.75" customWidth="1"/>
     <col min="6" max="6" width="56" customWidth="1"/>
     <col min="7" max="7" width="23.5" customWidth="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model_info[生物模型详情信息] .xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model_info[生物模型详情信息] .xlsx
@@ -5340,7 +5340,6 @@
       <c r="E139" t="s">
         <v>123</v>
       </c>
-      <c r="F139"/>
       <c r="G139" t="s">
         <v>207</v>
       </c>
@@ -5361,7 +5360,6 @@
       <c r="E140" t="s">
         <v>131</v>
       </c>
-      <c r="F140"/>
       <c r="G140" t="s">
         <v>208</v>
       </c>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model_info[生物模型详情信息] .xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model_info[生物模型详情信息] .xlsx
@@ -1411,27 +1411,27 @@
       </c>
     </row>
     <row r="13" s="3">
-      <c r="A13" t="n">
+      <c r="A13" s="2" t="n">
         <v>1030009</v>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Hair/Hair_9</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>人类-发型</t>
         </is>
@@ -1835,13 +1835,13 @@
         <v>1050012</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -1859,13 +1859,13 @@
         <v>1050013</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1883,13 +1883,13 @@
         <v>1050014</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -2042,13 +2042,13 @@
         <v>1060006</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>0</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>0</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>0</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
